--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -13977,9 +13977,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -14027,9 +14033,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -14077,9 +14089,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1402</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -14127,9 +14145,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F473"/>
+  <dimension ref="A1:F474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11778,6 +11778,30 @@
       <c r="F473" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:38+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>305.37</v>
+      </c>
+      <c r="C474" t="n">
+        <v>173.48</v>
+      </c>
+      <c r="D474" t="n">
+        <v>181.57</v>
+      </c>
+      <c r="E474" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16935,6 +16959,16 @@
       </c>
       <c r="B514" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -17097,28 +17131,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9493503219941954</v>
+        <v>0.9487174781908448</v>
       </c>
       <c r="J2" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04737943628355001</v>
+        <v>0.04752444707875658</v>
       </c>
       <c r="M2" t="n">
-        <v>18.79134610577061</v>
+        <v>18.75640871567712</v>
       </c>
       <c r="N2" t="n">
-        <v>1060.003233387356</v>
+        <v>1057.757849007932</v>
       </c>
       <c r="O2" t="n">
-        <v>32.55769084851313</v>
+        <v>32.52318940399191</v>
       </c>
       <c r="P2" t="n">
-        <v>281.8627117126417</v>
+        <v>281.8690316046678</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17169,28 +17203,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2756373717438253</v>
+        <v>0.2727813160186733</v>
       </c>
       <c r="J3" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K3" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08723361066905266</v>
+        <v>0.08576844957319596</v>
       </c>
       <c r="M3" t="n">
-        <v>4.55070555578748</v>
+        <v>4.553793858086688</v>
       </c>
       <c r="N3" t="n">
-        <v>46.52079790147437</v>
+        <v>46.52700383695358</v>
       </c>
       <c r="O3" t="n">
-        <v>6.820615654138149</v>
+        <v>6.821070578505517</v>
       </c>
       <c r="P3" t="n">
-        <v>173.2512319198997</v>
+        <v>173.2797426242448</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17241,28 +17275,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2418021760781779</v>
+        <v>0.2397317443256927</v>
       </c>
       <c r="J4" t="n">
+        <v>473</v>
+      </c>
+      <c r="K4" t="n">
         <v>472</v>
       </c>
-      <c r="K4" t="n">
-        <v>471</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1112944428941229</v>
+        <v>0.1098519344484788</v>
       </c>
       <c r="M4" t="n">
-        <v>4.162089456537619</v>
+        <v>4.161760433199202</v>
       </c>
       <c r="N4" t="n">
-        <v>27.26896235312123</v>
+        <v>27.26621212860383</v>
       </c>
       <c r="O4" t="n">
-        <v>5.221969202620906</v>
+        <v>5.221705863853672</v>
       </c>
       <c r="P4" t="n">
-        <v>180.30169955565</v>
+        <v>180.3223827301714</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17313,28 +17347,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1094179991277682</v>
+        <v>0.1119793039955936</v>
       </c>
       <c r="J5" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003586931276084115</v>
+        <v>0.003771575412097161</v>
       </c>
       <c r="M5" t="n">
-        <v>10.78953141734027</v>
+        <v>10.78111716426849</v>
       </c>
       <c r="N5" t="n">
-        <v>195.4610880061946</v>
+        <v>195.132803436153</v>
       </c>
       <c r="O5" t="n">
-        <v>13.98073989480509</v>
+        <v>13.96899436023055</v>
       </c>
       <c r="P5" t="n">
-        <v>217.8464216217076</v>
+        <v>217.820962044211</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17372,7 +17406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F473"/>
+  <dimension ref="A1:F474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32491,6 +32525,38 @@
         </is>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:38+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-46.890467403187984,168.1344205119393</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-46.890550707019756,168.13240278070413</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-46.89122039895189,168.1320077662169</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-46.89204693599815,168.13204677528907</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F474"/>
+  <dimension ref="A1:F476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11802,6 +11802,54 @@
       <c r="F474" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:36+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="C475" t="n">
+        <v>179.38</v>
+      </c>
+      <c r="D475" t="n">
+        <v>183.06</v>
+      </c>
+      <c r="E475" t="n">
+        <v>220.87</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>309.42</v>
+      </c>
+      <c r="C476" t="n">
+        <v>179.49</v>
+      </c>
+      <c r="D476" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="E476" t="n">
+        <v>219.79</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11816,7 +11864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16969,6 +17017,26 @@
       </c>
       <c r="B515" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -17131,28 +17199,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9487174781908448</v>
+        <v>0.9490717253585821</v>
       </c>
       <c r="J2" t="n">
+        <v>475</v>
+      </c>
+      <c r="K2" t="n">
         <v>473</v>
       </c>
-      <c r="K2" t="n">
-        <v>471</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04752444707875658</v>
+        <v>0.04797865378845667</v>
       </c>
       <c r="M2" t="n">
-        <v>18.75640871567712</v>
+        <v>18.68412538071231</v>
       </c>
       <c r="N2" t="n">
-        <v>1057.757849007932</v>
+        <v>1053.300890137364</v>
       </c>
       <c r="O2" t="n">
-        <v>32.52318940399191</v>
+        <v>32.45459736520181</v>
       </c>
       <c r="P2" t="n">
-        <v>281.8690316046678</v>
+        <v>281.865449926973</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17203,28 +17271,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2727813160186733</v>
+        <v>0.2718916906655428</v>
       </c>
       <c r="J3" t="n">
+        <v>475</v>
+      </c>
+      <c r="K3" t="n">
         <v>473</v>
       </c>
-      <c r="K3" t="n">
-        <v>471</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.08576844957319596</v>
+        <v>0.08597390697952934</v>
       </c>
       <c r="M3" t="n">
-        <v>4.553793858086688</v>
+        <v>4.538421006417558</v>
       </c>
       <c r="N3" t="n">
-        <v>46.52700383695358</v>
+        <v>46.3353000872478</v>
       </c>
       <c r="O3" t="n">
-        <v>6.821070578505517</v>
+        <v>6.807003752551323</v>
       </c>
       <c r="P3" t="n">
-        <v>173.2797426242448</v>
+        <v>173.2886949015193</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17275,28 +17343,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2397317443256927</v>
+        <v>0.2361087490460292</v>
       </c>
       <c r="J4" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K4" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1098519344484788</v>
+        <v>0.1074936511632292</v>
       </c>
       <c r="M4" t="n">
-        <v>4.161760433199202</v>
+        <v>4.159007171171542</v>
       </c>
       <c r="N4" t="n">
-        <v>27.26621212860383</v>
+        <v>27.23701557537918</v>
       </c>
       <c r="O4" t="n">
-        <v>5.221705863853672</v>
+        <v>5.218909423948569</v>
       </c>
       <c r="P4" t="n">
-        <v>180.3223827301714</v>
+        <v>180.3588747548099</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17347,28 +17415,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1119793039955936</v>
+        <v>0.1116023148062873</v>
       </c>
       <c r="J5" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K5" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003771575412097161</v>
+        <v>0.003780926007324714</v>
       </c>
       <c r="M5" t="n">
-        <v>10.78111716426849</v>
+        <v>10.73786338302112</v>
       </c>
       <c r="N5" t="n">
-        <v>195.132803436153</v>
+        <v>194.3133273983709</v>
       </c>
       <c r="O5" t="n">
-        <v>13.96899436023055</v>
+        <v>13.9396315373962</v>
       </c>
       <c r="P5" t="n">
-        <v>217.820962044211</v>
+        <v>217.8247441717748</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17406,7 +17474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F474"/>
+  <dimension ref="A1:F476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32557,6 +32625,70 @@
         </is>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:36+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-46.890468492333085,168.13442352604028</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-46.8905754233957,168.13247117672017</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-46.89122664095341,168.13202503926175</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-46.89202083684933,168.13197455203752</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>-46.890484368708876,168.13446746237315</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>-46.89057588420911,168.13247245190075</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-46.891219686777056,168.13200579546708</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-46.892016312433896,168.13196203180232</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F476"/>
+  <dimension ref="A1:F477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11850,6 +11850,30 @@
       <c r="F476" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>309.34</v>
+      </c>
+      <c r="C477" t="n">
+        <v>179.39</v>
+      </c>
+      <c r="D477" t="n">
+        <v>180.49</v>
+      </c>
+      <c r="E477" t="n">
+        <v>218.08</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17037,6 +17061,16 @@
       </c>
       <c r="B517" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -17199,28 +17233,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9490717253585821</v>
+        <v>0.9499597931760658</v>
       </c>
       <c r="J2" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K2" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04797865378845667</v>
+        <v>0.04827476726266122</v>
       </c>
       <c r="M2" t="n">
-        <v>18.68412538071231</v>
+        <v>18.64707414071837</v>
       </c>
       <c r="N2" t="n">
-        <v>1053.300890137364</v>
+        <v>1051.08883575763</v>
       </c>
       <c r="O2" t="n">
-        <v>32.45459736520181</v>
+        <v>32.42050023916395</v>
       </c>
       <c r="P2" t="n">
-        <v>281.865449926973</v>
+        <v>281.8564915253752</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17271,28 +17305,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2718916906655428</v>
+        <v>0.2714325814899154</v>
       </c>
       <c r="J3" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K3" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08597390697952934</v>
+        <v>0.0860655446698918</v>
       </c>
       <c r="M3" t="n">
-        <v>4.538421006417558</v>
+        <v>4.53083591962799</v>
       </c>
       <c r="N3" t="n">
-        <v>46.3353000872478</v>
+        <v>46.24024596004904</v>
       </c>
       <c r="O3" t="n">
-        <v>6.807003752551323</v>
+        <v>6.800018085273674</v>
       </c>
       <c r="P3" t="n">
-        <v>173.2886949015193</v>
+        <v>173.2933243496742</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17343,28 +17377,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2361087490460292</v>
+        <v>0.2336168919269817</v>
       </c>
       <c r="J4" t="n">
+        <v>476</v>
+      </c>
+      <c r="K4" t="n">
         <v>475</v>
       </c>
-      <c r="K4" t="n">
-        <v>474</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1074936511632292</v>
+        <v>0.1056345723509509</v>
       </c>
       <c r="M4" t="n">
-        <v>4.159007171171542</v>
+        <v>4.160396368703982</v>
       </c>
       <c r="N4" t="n">
-        <v>27.23701557537918</v>
+        <v>27.25899770485971</v>
       </c>
       <c r="O4" t="n">
-        <v>5.218909423948569</v>
+        <v>5.221015007147529</v>
       </c>
       <c r="P4" t="n">
-        <v>180.3588747548099</v>
+        <v>180.3840188491361</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17415,28 +17449,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1116023148062873</v>
+        <v>0.1105090947128883</v>
       </c>
       <c r="J5" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K5" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003780926007324714</v>
+        <v>0.003724205534775704</v>
       </c>
       <c r="M5" t="n">
-        <v>10.73786338302112</v>
+        <v>10.72057376904884</v>
       </c>
       <c r="N5" t="n">
-        <v>194.3133273983709</v>
+        <v>193.9205092967103</v>
       </c>
       <c r="O5" t="n">
-        <v>13.9396315373962</v>
+        <v>13.92553443486857</v>
       </c>
       <c r="P5" t="n">
-        <v>217.8247441717748</v>
+        <v>217.8357210299055</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17474,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F476"/>
+  <dimension ref="A1:F477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32689,6 +32723,38 @@
         </is>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>-46.89048403358766,168.13446653495689</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>-46.890575465287824,168.13247129264565</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-46.89121587454655,168.13199524616016</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-46.8920091487735,168.131942208101</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -11888,7 +11888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17071,6 +17071,16 @@
       </c>
       <c r="B518" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F477"/>
+  <dimension ref="A1:F480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11872,6 +11872,78 @@
         <v>218.08</v>
       </c>
       <c r="F477" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>309.14</v>
+      </c>
+      <c r="C478" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="D478" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="E478" t="n">
+        <v>214.24</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>309.89</v>
+      </c>
+      <c r="C479" t="n">
+        <v>183.73</v>
+      </c>
+      <c r="D479" t="n">
+        <v>184.02</v>
+      </c>
+      <c r="E479" t="n">
+        <v>214.96</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>308.97</v>
+      </c>
+      <c r="C480" t="n">
+        <v>183.73</v>
+      </c>
+      <c r="D480" t="n">
+        <v>184.02</v>
+      </c>
+      <c r="E480" t="n">
+        <v>214.96</v>
+      </c>
+      <c r="F480" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11888,7 +11960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17081,6 +17153,36 @@
       </c>
       <c r="B519" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -17243,28 +17345,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9499597931760658</v>
+        <v>0.9523839146305145</v>
       </c>
       <c r="J2" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K2" t="n">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04827476726266122</v>
+        <v>0.04915915051976316</v>
       </c>
       <c r="M2" t="n">
-        <v>18.64707414071837</v>
+        <v>18.53613652367987</v>
       </c>
       <c r="N2" t="n">
-        <v>1051.08883575763</v>
+        <v>1044.503977763058</v>
       </c>
       <c r="O2" t="n">
-        <v>32.42050023916395</v>
+        <v>32.31878676192932</v>
       </c>
       <c r="P2" t="n">
-        <v>281.8564915253752</v>
+        <v>281.8318346737975</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17315,28 +17417,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2714325814899154</v>
+        <v>0.2738721707051402</v>
       </c>
       <c r="J3" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K3" t="n">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0860655446698918</v>
+        <v>0.08853614219465289</v>
       </c>
       <c r="M3" t="n">
-        <v>4.53083591962799</v>
+        <v>4.518187978660668</v>
       </c>
       <c r="N3" t="n">
-        <v>46.24024596004904</v>
+        <v>45.99084174936758</v>
       </c>
       <c r="O3" t="n">
-        <v>6.800018085273674</v>
+        <v>6.781654794323254</v>
       </c>
       <c r="P3" t="n">
-        <v>173.2933243496742</v>
+        <v>173.2685032223985</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17387,28 +17489,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2336168919269817</v>
+        <v>0.2293244413554556</v>
       </c>
       <c r="J4" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K4" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1056345723509509</v>
+        <v>0.1031738618306126</v>
       </c>
       <c r="M4" t="n">
-        <v>4.160396368703982</v>
+        <v>4.151430663611571</v>
       </c>
       <c r="N4" t="n">
-        <v>27.25899770485971</v>
+        <v>27.17615388830858</v>
       </c>
       <c r="O4" t="n">
-        <v>5.221015007147529</v>
+        <v>5.213075281281537</v>
       </c>
       <c r="P4" t="n">
-        <v>180.3840188491361</v>
+        <v>180.4276749773096</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17459,28 +17561,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1105090947128883</v>
+        <v>0.1032054533984388</v>
       </c>
       <c r="J5" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K5" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003724205534775704</v>
+        <v>0.003291498527893677</v>
       </c>
       <c r="M5" t="n">
-        <v>10.72057376904884</v>
+        <v>10.68782491717577</v>
       </c>
       <c r="N5" t="n">
-        <v>193.9205092967103</v>
+        <v>192.9332828338664</v>
       </c>
       <c r="O5" t="n">
-        <v>13.92553443486857</v>
+        <v>13.89004257854764</v>
       </c>
       <c r="P5" t="n">
-        <v>217.8357210299055</v>
+        <v>217.9096605377993</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17518,7 +17620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F477"/>
+  <dimension ref="A1:F480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32765,6 +32867,102 @@
         </is>
       </c>
     </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>-46.89048319578456,168.13446421641623</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>-46.89057927747116,168.13248184186753</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>-46.89121905838747,168.13200405657022</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-46.89199306194527,168.1318976917392</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>-46.89048633754592,168.13447291094403</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>-46.890593646461625,168.1325216043332</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-46.89123066264436,168.13203616820562</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-46.891996078226825,168.13190603855492</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-46.8904824836519,168.13446224565678</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-46.890593646461625,168.1325216043332</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-46.89123066264436,168.13203616820562</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-46.891996078226825,168.13190603855492</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F480"/>
+  <dimension ref="A1:F484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11944,6 +11944,102 @@
         <v>214.96</v>
       </c>
       <c r="F480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>310.11</v>
+      </c>
+      <c r="C481" t="n">
+        <v>187.71</v>
+      </c>
+      <c r="D481" t="n">
+        <v>184.71</v>
+      </c>
+      <c r="E481" t="n">
+        <v>213.17</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>311.04</v>
+      </c>
+      <c r="C482" t="n">
+        <v>185.06</v>
+      </c>
+      <c r="D482" t="n">
+        <v>183.94</v>
+      </c>
+      <c r="E482" t="n">
+        <v>212.64</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>310.29</v>
+      </c>
+      <c r="C483" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="D483" t="n">
+        <v>183.32</v>
+      </c>
+      <c r="E483" t="n">
+        <v>211.45</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>309.34</v>
+      </c>
+      <c r="C484" t="n">
+        <v>180.39</v>
+      </c>
+      <c r="D484" t="n">
+        <v>183.64</v>
+      </c>
+      <c r="E484" t="n">
+        <v>212.34</v>
+      </c>
+      <c r="F484" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11960,7 +12056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17183,6 +17279,46 @@
       </c>
       <c r="B522" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -17345,28 +17481,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9523839146305145</v>
+        <v>0.9567264971254202</v>
       </c>
       <c r="J2" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="K2" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04915915051976316</v>
+        <v>0.05045603887962591</v>
       </c>
       <c r="M2" t="n">
-        <v>18.53613652367987</v>
+        <v>18.39344213041025</v>
       </c>
       <c r="N2" t="n">
-        <v>1044.503977763058</v>
+        <v>1035.882187473358</v>
       </c>
       <c r="O2" t="n">
-        <v>32.31878676192932</v>
+        <v>32.18512369827648</v>
       </c>
       <c r="P2" t="n">
-        <v>281.8318346737975</v>
+        <v>281.7875131322216</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17417,28 +17553,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2738721707051402</v>
+        <v>0.2797228168788345</v>
       </c>
       <c r="J3" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="K3" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08853614219465289</v>
+        <v>0.09324134163291564</v>
       </c>
       <c r="M3" t="n">
-        <v>4.518187978660668</v>
+        <v>4.516999310978342</v>
       </c>
       <c r="N3" t="n">
-        <v>45.99084174936758</v>
+        <v>45.777029399386</v>
       </c>
       <c r="O3" t="n">
-        <v>6.781654794323254</v>
+        <v>6.765872404899903</v>
       </c>
       <c r="P3" t="n">
-        <v>173.2685032223985</v>
+        <v>173.208839743604</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17489,28 +17625,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2293244413554556</v>
+        <v>0.2250638050875619</v>
       </c>
       <c r="J4" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="K4" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1031738618306126</v>
+        <v>0.101212115866535</v>
       </c>
       <c r="M4" t="n">
-        <v>4.151430663611571</v>
+        <v>4.13373171961933</v>
       </c>
       <c r="N4" t="n">
-        <v>27.17615388830858</v>
+        <v>27.0115767488902</v>
       </c>
       <c r="O4" t="n">
-        <v>5.213075281281537</v>
+        <v>5.197266276504427</v>
       </c>
       <c r="P4" t="n">
-        <v>180.4276749773096</v>
+        <v>180.4711796211397</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17561,28 +17697,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1032054533984388</v>
+        <v>0.09018510025361533</v>
       </c>
       <c r="J5" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="K5" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003291498527893677</v>
+        <v>0.002554350025688712</v>
       </c>
       <c r="M5" t="n">
-        <v>10.68782491717577</v>
+        <v>10.660538514935</v>
       </c>
       <c r="N5" t="n">
-        <v>192.9332828338664</v>
+        <v>191.8921855848371</v>
       </c>
       <c r="O5" t="n">
-        <v>13.89004257854764</v>
+        <v>13.8525154966467</v>
       </c>
       <c r="P5" t="n">
-        <v>217.9096605377993</v>
+        <v>218.0419529507325</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17620,7 +17756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F480"/>
+  <dimension ref="A1:F484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32963,6 +33099,134 @@
         </is>
       </c>
     </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-46.890487259129145,168.13447546133904</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-46.890610319501214,168.1325677427321</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-46.891233553234116,168.1320441671351</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-46.89198857941471,168.13188528744539</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:03+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>-46.89049115491213,168.1344862425553</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>-46.89059921810748,168.13253702243804</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>-46.8912303275035,168.13203524079356</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-46.891986359095355,168.13187914326326</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>-46.890488013151725,168.13447754802593</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>-46.89059561538932,168.13252705283602</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>-46.89122773016148,168.13202805335055</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-46.89198137384886,168.13186534783745</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>-46.89048403358766,168.13446653495689</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>-46.890579654500236,168.13248288519728</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>-46.89122907072515,168.13203176299848</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-46.89198510231067,168.13187566542456</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
